--- a/高橋将史商会_商品群別ニュース収集フォーマット.xlsx
+++ b/高橋将史商会_商品群別ニュース収集フォーマット.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,8 +115,14 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="007D6608"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +225,12 @@
         <bgColor rgb="00FFD9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -238,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -331,6 +343,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,7 +752,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>収集期間：2026-04-18〜2026-04-24　　担当者名：Claude Code週次レポート　　注目テーマ：中東・ホルムズ海峡情勢</t>
+          <t>収集期間：2026-05-01〜2026-05-07　　担当者名：Claude Code週次レポート　　注目テーマ：中東・ホルムズ海峡情勢</t>
         </is>
       </c>
     </row>
@@ -897,92 +912,92 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>古紙・クラフト紙は国内調達主体で比較的安定を維持。ただし重油・電力コストがさらに上昇</t>
+          <t>古紙・クラフト紙は国内調達中心で原油高影響軽微。ただし輸入OCC（古紙）輸送費上昇で+5〜8%程度の価格上昇圧力。</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>仕入値+7〜10%見込み。エネルギーサーチャージが追加計上</t>
+          <t>5月に一部メーカーが段ボールシートを+5〜10%値上げ通知。燃料費・電力コスト上昇が主因。</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>国内主体（中越パルプ、王子HD等）</t>
+          <t>国内古紙リサイクル中心（95%以上）。一部輸入クラフトパルプを使用。</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>国内代替十分。緊急調達不要</t>
+          <t>国内メーカー複数社との分散調達。国産クラフトパルプへの切替検討。</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>直接影響小。輸送・製造エネルギーコスト上昇が主因</t>
+          <t>直接的な原材料依存は低い。ただし輸送燃料コスト増で配送コストが+10〜15%上昇。</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>間接影響（エネルギーコスト上昇→製造コスト増）</t>
+          <t>間接的：燃料費・物流コスト増による製造原価上昇。</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>直接依存なし。ただし重油・電力コスト上昇で製造コスト増</t>
+          <t>段ボール製造における石油系副資材（接着剤・コーティング剤）コストが+15〜20%上昇。</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>燃料サーチャージ+18〜22%</t>
+          <t>アジア発着コンテナ運賃は前年比+40〜60%水準継続。輸入原材料の仕入コスト増。</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>軽油価格上昇で配送コスト+8〜12%</t>
+          <t>軽油価格上昇でトラック配送コスト+10〜12%。大口顧客への配送頻度見直し検討。</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>大きな変動なし（国内調達中心）</t>
+          <t>国内調達中心のため比較的安定。2〜3週間程度。一部輸入品は+1〜2週間延長。</t>
         </is>
       </c>
       <c r="M4" s="14" t="inlineStr">
         <is>
-          <t>輸入原材料（クラフトパルプ）に若干影響。¥158で前週比悪化</t>
+          <t>輸入比率低いため為替影響は限定的（+3〜5%程度）。</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
         <is>
-          <t>+7〜12%</t>
+          <t>+8〜10%（燃料・輸送費込み）</t>
         </is>
       </c>
       <c r="O4" s="12" t="inlineStr">
         <is>
-          <t>食品メーカー向け需要は安定。在庫積み増し動きが継続</t>
+          <t>食品・Eコマース向け需要は底堅い。製造業向けは若干軟化。</t>
         </is>
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>特になし</t>
+          <t>プラスチック削減のトレンドで段ボール代替需要は中長期で増加見込み。</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr">
         <is>
-          <t>同業他社も輸送コスト転嫁を実施開始</t>
+          <t>王子HD・レンゴー等が5月値上げ実施。業界全体で価格転嫁の動き。</t>
         </is>
       </c>
       <c r="R4" s="14" t="inlineStr">
         <is>
-          <t>5月より価格改定を実施予定。顧客へ通知済み</t>
+          <t>食品メーカー・量販店への納品価格改定交渉が必要。</t>
         </is>
       </c>
       <c r="S4" s="14" t="inlineStr">
         <is>
-          <t>概ね正常。1〜2ヶ月分確保済み</t>
+          <t>在庫は通常水準。原材料は4〜6週分確保推奨。</t>
         </is>
       </c>
       <c r="T4" s="14" t="inlineStr">
         <is>
-          <t>5月の価格改定を予定通り実施。燃料サーチャージ明細を顧客に提示し透明性を確保</t>
+          <t>5月末までに主要顧客への価格改定通知を完了。複数サプライヤーとの在庫確保契約を締結。</t>
         </is>
       </c>
       <c r="U4" s="30" t="inlineStr">
@@ -992,17 +1007,17 @@
       </c>
       <c r="V4" s="16" t="inlineStr">
         <is>
-          <t>日本包装技術協会、荷主協会</t>
+          <t>日本製紙連合会、王子HD・レンゴー各社IR、日本経済新聞2026年5月</t>
         </is>
       </c>
       <c r="W4" s="16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X4" s="16" t="inlineStr">
         <is>
-          <t>石油系製品と比較すると影響は軽微。価格転嫁交渉は進展中</t>
+          <t>ホルムズ影響は間接的。燃料費・物流コスト増が主な価格上昇要因。</t>
         </is>
       </c>
     </row>
@@ -1019,92 +1034,92 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>スチレンモノマー価格が前週比さらに+5%上昇。ナフサ+48%を完全に転嫁</t>
+          <t>スチレンモノマー：ナフサ高騰直撃。4〜6月期スチレン価格はナフサ連動で前期比+45〜50%見込み。PSジャパン・東洋スチレン等が5月値上げ通知。</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>仕入値+40〜48%見込み。PSジャパンが5月出荷分から追加値上げを通知</t>
+          <t>発泡スチロール製品：5月から+25〜35%の大幅値上げ実施中。魚箱・食品容器向けも例外なし。</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>PSジャパン、旭化成等（ナフサは中東依存60〜70%）</t>
+          <t>国内PSメーカー（PSジャパン・東洋スチレン・DICスチレン）。スチレンモノマーは中東産ナフサ由来。</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>北米産スチレンモノマーの代替調達：Styrolutionと試験調達交渉中</t>
+          <t>紙製容器・段ボールへの一部切替可能だが断熱性・軽量性で代替困難。バイオ系発泡材は価格高騰中。</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>深刻継続。原料ナフサ供給逼迫で生産縮小の動きが加速</t>
+          <t>ナフサ→スチレンモノマー→PSという原料チェーンがホルムズ封鎖に直結。原料調達コスト+48%超。</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>スチレンモノマー供給不足が深刻化。5月以降の入手困難が確定的</t>
+          <t>中東産ナフサの供給途絶が直接的影響。国内エチレン設備12基中6基が減産中。</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>ブレント$125/bbl。ナフサCIF Japan +48%</t>
+          <t>スチレンモノマーはナフサから直接製造。ナフサCIF +48%がダイレクトに製品価格へ転嫁。</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>タンカー運賃$10.2Mまで上昇</t>
+          <t>中東産ナフサ輸送：タンカー保険料が通常の3〜5倍。調達コストに上乗せ。</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>燃料費上昇で+8〜12%</t>
+          <t>国内配送コスト+10〜12%。重量物のため軽油価格影響が大きい。</t>
         </is>
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>3ヶ月以上の遅延リスク。5月分は確保不透明</t>
+          <t>原料確保難で国内PSメーカーの生産調整継続。納期が通常4週から6〜8週に延長。</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>ナフサ輸入コスト：¥155/USD水準で輸入原価+15〜20%の為替影響。</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>+45〜55%</t>
+          <t>+40〜50%（原料高+為替影響+運賃合算）</t>
         </is>
       </c>
       <c r="O5" s="17" t="inlineStr">
         <is>
-          <t>食品メーカーの紙製代替トレーへの切替えが加速</t>
+          <t>水産業・青果市場向けは代替困難で需要維持。食品製造向けに軽量代替品の引合増加。</t>
         </is>
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t>特になし</t>
+          <t>発泡スチロール規制の動向を注視。現時点で即時規制なし。</t>
         </is>
       </c>
       <c r="Q5" s="17" t="inlineStr">
         <is>
-          <t>在庫争奪戦が激化。一部商社が受注停止</t>
+          <t>競合各社も同条件で値上げ。製品供給量は絞り込み傾向。</t>
         </is>
       </c>
       <c r="R5" s="14" t="inlineStr">
         <is>
-          <t>追加価格改定と代替品提案を至急実施</t>
+          <t>水産業・スーパー等への価格改定は避けられない。代替品提案を同時に準備。</t>
         </is>
       </c>
       <c r="S5" s="14" t="inlineStr">
         <is>
-          <t>4ヶ月分以上の積み増しが急務</t>
+          <t>在庫は2〜3週分に低下。至急4〜6週分への積み増しが必要。</t>
         </is>
       </c>
       <c r="T5" s="14" t="inlineStr">
         <is>
-          <t>Styrolutionとの北米代替調達を今週中に決定。3ヶ月以上の在庫確保を優先。5月値上げ通知を顧客に発送</t>
+          <t>【緊急】今週中にPSジャパン・東洋スチレンに4〜6月分の発注量を確定。在庫を6週分に積増し。顧客への価格改定通知を5月15日までに完了。</t>
         </is>
       </c>
       <c r="U5" s="31" t="inlineStr">
@@ -1114,17 +1129,17 @@
       </c>
       <c r="V5" s="17" t="inlineStr">
         <is>
-          <t>化学工業日報、Plastics News、ICIS</t>
+          <t>PSジャパン・東洋スチレン値上げ通知、石油化学工業協会2026年5月、化学工業日報</t>
         </is>
       </c>
       <c r="W5" s="17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X5" s="17" t="inlineStr">
         <is>
-          <t>5月以降の供給不足が確実視される。代替品提案で顧客離れを防止</t>
+          <t>ホルムズ封鎖の直撃商品。原料チェーンが中東ナフサに直結。6月以降更なる値上げ可能性あり。</t>
         </is>
       </c>
     </row>
@@ -1141,92 +1156,92 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>PS・PP樹脂ともに+40〜50%。エフピコが5月出荷分の値上げを正式通知</t>
+          <t>PS（ポリスチレン）・PP（ポリプロピレン）ともに前期比+30〜45%の大幅値上げ。旭化成PE全製品+120円/kg実施、PP・PSも同様の値上げ圧力。</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>仕入値+40〜50%見込み。6月以降も追加値上げリスク</t>
+          <t>食品トレー製品：5月から+20〜30%値上げ。スーパー・食品メーカーとの価格改定交渉が急務。</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>エフピコ、中央化学等（樹脂はナフサ依存60〜70%）</t>
+          <t>住友化学・旭化成・三井化学等国内石化メーカー。原料はナフサ由来PP・PS・PET。</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>バガス製・紙製トレーへの代替：一部顧客で試験導入開始</t>
+          <t>紙製トレーへの切替検討中だが食品安全性・コスト面で課題。バイオPP・リサイクルPPは供給量不足。</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>深刻継続。PS・PP樹脂の原料調達が更なる逼迫</t>
+          <t>PP・PS原料がナフサ由来。ホルムズ封鎖→ナフサ高騰→樹脂価格+35〜45%の直接影響。</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>中東産PS/PP樹脂の84%が依然として供給困難</t>
+          <t>中東産ナフサの代替（米国産・東南アジア産）調達も価格高騰・運賃増で総コストは同等以上。</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>ナフサ価格+48%が直撃</t>
+          <t>エチレン→PP、スチレン→PSの製造ライン：ナフサ+48%が直接原価に反映。</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>タンカー運賃が前週比さらに上昇</t>
+          <t>輸入トレーのアジア発着運賃+50〜70%。国内メーカー品でも原料輸入コスト転嫁。</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>+8〜12%</t>
+          <t>冷蔵配送向けトレーの輸送コスト+12〜15%。</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>3ヶ月以上の遅延リスク</t>
+          <t>国内生産ラインの稼働率低下で4週→6週に延長。輸入品は8〜10週に延長。</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>樹脂輸入コスト：¥155/USD水準で+15〜20%の為替影響。</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
         <is>
-          <t>+42〜52%</t>
+          <t>+35〜45%（原料高+運賃+為替）</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>大手スーパー・食品メーカーで紙トレーへの切替えが本格化</t>
+          <t>スーパー・食品製造向けは代替困難で需要維持。ただし価格高騰で内容量調整（ステルス値上げ）の動き。</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>環境配慮型包材への移行要求が強まる</t>
+          <t>食品用プラスチック代替促進法の動向注視。紙製への切替促進が強まる可能性。</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>代替素材の在庫確保でも競合激化</t>
+          <t>大手トレーメーカー（エフピコ等）が同時期に値上げ通知。供給絞り込み傾向。</t>
         </is>
       </c>
       <c r="R6" s="14" t="inlineStr">
         <is>
-          <t>価格転嫁と代替品提案の両輪で対応。顧客への個別訪問を実施中</t>
+          <t>スーパー・食品メーカーへの価格転嫁交渉が最重要課題。代替品提案との抱き合わせで合意形成。</t>
         </is>
       </c>
       <c r="S6" s="14" t="inlineStr">
         <is>
-          <t>4ヶ月分以上の積み増しが急務</t>
+          <t>在庫は3〜4週分。5〜6週分への積み増しを推奨。</t>
         </is>
       </c>
       <c r="T6" s="14" t="inlineStr">
         <is>
-          <t>エフピコとの在庫確保交渉を本週完了。バガス製トレーのサンプルを主要5社に提供。価格改定通知を全顧客に発送</t>
+          <t>【緊急】主要樹脂メーカーへの6月分発注を今週中に確定。エフピコ等複数ソースへの分散調達体制強化。価格改定通知を5月20日までに発送。</t>
         </is>
       </c>
       <c r="U6" s="31" t="inlineStr">
@@ -1236,17 +1251,17 @@
       </c>
       <c r="V6" s="16" t="inlineStr">
         <is>
-          <t>化学工業日報、Packaging Dive、Food Navigator</t>
+          <t>旭化成値上げ通知、住友化学・三井化学IR、エフピコ決算資料、化学工業日報2026年5月</t>
         </is>
       </c>
       <c r="W6" s="16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X6" s="16" t="inlineStr">
         <is>
-          <t>顧客側の代替需要獲得チャンスでもある。代替品提案を積極化</t>
+          <t>発泡スチロールと同様にナフサ直撃商品。スーパー向け納入比率が高いため早急な価格交渉が必要。</t>
         </is>
       </c>
     </row>
@@ -1263,92 +1278,92 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>PE樹脂（LDPE/LLDPE）がナフサ連動で+40%に達する</t>
+          <t>LLDPE・LDPE原料：旭化成が全製品+120円/kg値上げ実施。5月下旬以降30%超の追加値上げ見込み。PE全般で供給逼迫。</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>仕入値+38〜45%見込み。住友化学が5月出荷分の追加値上げを通知</t>
+          <t>ボードン袋（ポリ袋・青果袋）：5月から+20〜28%値上げ。農産物直売所・スーパー向けに影響大。</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>住友化学、LG化学等（PE樹脂は中東依存高）</t>
+          <t>旭化成・住友化学・丸紅（輸入PE）。原料はエチレン由来LLDPE・LDPE。</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>北米産LDPEとの代替契約：ExxonMobilと価格交渉中</t>
+          <t>バイオPE（サトウキビ由来）は価格3倍・供給量限定。再生PE使用も食品用途では規制あり。</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>深刻継続。中東産PE樹脂の供給制限が拡大</t>
+          <t>エチレン→PEの製造ラインが中東ナフサに依存。ホルムズ封鎖→エチレン設備6基減産→PE供給不足直撃。</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>中東産ポリエチレン輸出の大部分がホルムズ経由で依然停止</t>
+          <t>中東からのナフサ供給途絶。国内石化12基中6基減産継続。輸入LDPEも運賃+50%で代替困難。</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>エチレン→ナフサ連動。ナフサ+48%が直撃</t>
+          <t>エチレンはナフサ由来。ナフサ+48%がPE原価に直結。エチレン設備減産で国内供給量も▼20%。</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>タンカー運賃$10.2Mまで上昇</t>
+          <t>輸入PE（東南アジア・米国産）の海上運賃+50〜70%。代替調達でも総コスト増。</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>+8〜12%</t>
+          <t>軽量製品のため物流コスト影響は相対的に小さいが+8〜10%増。</t>
         </is>
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>90日以上の遅延継続</t>
+          <t>国内PE生産量減少で通常3週→5〜7週に延長。輸入品は10〜12週。</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>輸入PE：¥155/USD水準で+15〜20%の為替影響。国産品でも原料輸入コスト転嫁。</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>+40〜48%</t>
+          <t>+25〜35%（原料高+供給量減+為替）</t>
         </is>
       </c>
       <c r="O7" s="17" t="inlineStr">
         <is>
-          <t>青果・鮮魚業界の需要は安定。価格上昇への懸念が強い</t>
+          <t>農産物・食品向けは代替困難で需要維持。環境規制でバイオ系への移行促進圧力あり。</t>
         </is>
       </c>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t>プラ削減規制対応として生分解性袋の問い合わせが増加</t>
+          <t>プラスチック資源循環促進法の対象。無償配布禁止の流れが一部顧客に影響。</t>
         </is>
       </c>
       <c r="Q7" s="17" t="inlineStr">
         <is>
-          <t>北米代替ルートへの切替えが業界全体に広がる</t>
+          <t>国内袋メーカー各社が同時期に値上げ・供給絞り込み。</t>
         </is>
       </c>
       <c r="R7" s="14" t="inlineStr">
         <is>
-          <t>青果・鮮魚取引先に5月価格改定通知を今週発送</t>
+          <t>農産物直売所・スーパー青果部門への影響大。代替品（紙袋・バイオPE）の紹介も並行。</t>
         </is>
       </c>
       <c r="S7" s="14" t="inlineStr">
         <is>
-          <t>4ヶ月分以上の積み増しが急務</t>
+          <t>在庫は3〜4週分。6週分への積み増し推奨。旭化成への発注量確定が急務。</t>
         </is>
       </c>
       <c r="T7" s="14" t="inlineStr">
         <is>
-          <t>ExxonMobil北米産LDPEの価格交渉を今週中に決着。生分解性ボードン袋のサンプル調達も並行実施</t>
+          <t>旭化成・丸紅への6月分ボードン袋原料発注を今週確定。バイオPE試作品の顧客提案を5月中に開始。価格改定通知を5月15日までに発送。</t>
         </is>
       </c>
       <c r="U7" s="31" t="inlineStr">
@@ -1358,17 +1373,17 @@
       </c>
       <c r="V7" s="17" t="inlineStr">
         <is>
-          <t>Plastics News、Plastics Today、METI</t>
+          <t>旭化成PE値上げ通知2026年5月、化学工業日報、プラスチック工業連盟</t>
         </is>
       </c>
       <c r="W7" s="17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X7" s="17" t="inlineStr">
         <is>
-          <t>北米代替品の価格は中東産比+5〜8%の見込み。コスト上昇は避けられないが供給安定化を優先</t>
+          <t>旭化成の+120円/kg値上げは即座に原価影響。6月以降の追加値上げも想定し先行在庫確保が必要。</t>
         </is>
       </c>
     </row>
@@ -1385,112 +1400,112 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>LLDPE樹脂スポット価格が$0.68/lbまで上昇。Dowが$0.12/lb追加値上げを通知</t>
+          <t>LLDPE原料：旭化成PE全製品+120円/kg値上げ実施。ストレッチフィルム向けLLDPEは需要高く供給逼迫。前期比+30〜40%の価格上昇圧力。</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>仕入値+40〜50%見込み。6月以降も上昇継続見通し</t>
+          <t>ストレッチフィルム（手巻き・機械巻き）：5月から+18〜25%値上げ。物流・小売向け需要は底堅い。</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>宇部興産、Dow等（LLDPE樹脂は中東依存高）</t>
+          <t>旭化成・住友化学・東ソー（国産LLDPE）。一部はサウジアラビア・UAE産輸入LLDPE。</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Dow・ExxonMobil北米産LLDPEの長期契約締結を優先交渉</t>
+          <t>再生LLDPEへの切替（食品接触用途では規制要確認）。バイオ系LLDPEは供給限定。</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>深刻継続。LLDPEの原料エチレン→ナフサルートが引き続き逼迫</t>
+          <t>輸入LLDPE（中東産）は供給途絶。国内エチレン設備減産でLLDPE供給も▼15〜20%。</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>中東産ポリエチレン供給減少が継続。需給逼迫が深刻化</t>
+          <t>サウジ・UAE産LLDPEの輸入ルート遮断。代替は米国・東南アジア産だが運賃+50%。</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>ナフサ+48%で原料コスト大幅上昇継続</t>
+          <t>LLDPE→エチレン→ナフサの原料チェーン。ナフサ+48%が製品原価に直結。</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>タンカー運賃が前週比さらに上昇</t>
+          <t>代替輸入品（米国・東南アジア産）の海上運賃+50〜70%。タンカー保険料増も加算。</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>+8〜12%</t>
+          <t>軽量・コンパクトで物流コスト影響は+8〜10%程度。</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>3ヶ月以上の遅延リスク継続</t>
+          <t>国内生産減少で通常2〜3週→4〜6週に延長。輸入品は8〜10週。</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>¥155/USD水準で輸入原料コスト+15〜20%の為替影響。</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>+40〜50%</t>
+          <t>+25〜35%（原料高+運賃+為替）</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>物流・食品加工向けの需要は安定。代替素材の問い合わせも増加</t>
+          <t>物流・小売・食品製造向けに需要堅調。代替品なく価格転嫁が必須。</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>特になし</t>
+          <t>プラスチック資源循環促進法対象。薄膜化・再生材混合の要請あり。</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Dow北米産への切替えが業界標準化しつつある</t>
+          <t>積水化学・タマポリ等が同時期に値上げ実施。市場全体で価格転嫁進行中。</t>
         </is>
       </c>
       <c r="R8" s="14" t="inlineStr">
         <is>
-          <t>物流・食品加工取引先に5月価格改定通知を発送予定</t>
+          <t>物流・小売各社への価格改定通知が必要。長期契約顧客には改定交渉を5月中に完了。</t>
         </is>
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>4ヶ月分以上の積み増しが急務</t>
+          <t>在庫は4週分程度。6週分への積み増し推奨。</t>
         </is>
       </c>
       <c r="T8" s="14" t="inlineStr">
         <is>
-          <t>Dowとの長期契約を本週中に締結。宇部興産への在庫積み増しも並行して依頼</t>
-        </is>
-      </c>
-      <c r="U8" s="31" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>旭化成・東ソーへの6月分LLDPE発注を今週確定。積水化学との安定供給契約締結を5月末までに完了。価格改定通知を5月20日までに発送。</t>
+        </is>
+      </c>
+      <c r="U8" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="V8" s="16" t="inlineStr">
         <is>
-          <t>Plastics Today、Plastics News、化学工業日報</t>
+          <t>旭化成PE値上げ通知、積水化学IR、化学工業日報2026年5月</t>
         </is>
       </c>
       <c r="W8" s="16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X8" s="16" t="inlineStr">
         <is>
-          <t>北米産への切替えは完了まで4〜8週間。5月末までの在庫ブリッジが鍵</t>
+          <t>中東産輸入LLDPEの代替調達が急務。国内在庫確保により短期的な供給安定化は可能。</t>
         </is>
       </c>
     </row>
@@ -1507,92 +1522,92 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>ブタジエン+78%（前週比さらに上昇）。WRP・Top Gloveが生産量前月比30%削減を正式発表</t>
+          <t>アクリロニトリル（AN）・ブタジエン原料：ナフサ高騰直撃で+40〜50%。マレーシア・タイ現地生産コストが急騰。手袋単価は前年比1.5倍水準。</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>仕入値+50〜60%見込み。$32/千枚まで上昇。6月以降の入手困難が確実視</t>
+          <t>ニトリル手袋（食品・医療向け）：5〜8月に本格高騰顕現化。箱単価が前年比+40〜60%の見込み。</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>マレーシア主体（WRP、Top Glove等）。両社が生産縮小を正式発表</t>
+          <t>マレーシア（Top Glove・Hartalega等）・タイ・ベトナム製。アジア産95%超。原料ANはナフサ由来。</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>タイ・Ansell製、ベトナム・SRITEXへの代替切替えを緊急実施中</t>
+          <t>天然ゴム手袋（ラテックス）への切替：アレルギーリスクで食品向けは困難。ビニール手袋は強度不足。PVC手袋は食品衛生法対応要確認。</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>極めて深刻。ブタジエン+78%急騰。マレーシア主要工場が生産30%削減</t>
+          <t>原料ANはナフサ由来。ホルムズ封鎖→ナフサ高騰→AN価格急騰→手袋製造コスト+40〜50%直撃。</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>5月末の在庫枯渇リスクが現実的。即時代替調達が不可欠</t>
+          <t>マレーシアQ2生産量の85%が北米市場向けに転換（高値売り）。アジア・日本向け供給量が▼60〜70%に激減。</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>ブタジエン→ナフサ連動。ナフサ+48%が直撃</t>
+          <t>アクリロニトリル：プロピレン（ナフサ由来）を原料とするアンモ酸化反応で製造。ナフサ高騰がAN価格を直撃。</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>東南アジア→日本の運賃も前週比上昇</t>
+          <t>マレーシア→日本の海上運賃：+60〜80%。コンテナ確保も困難化。</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>+8〜12%</t>
+          <t>国内配送は+8〜10%。特殊商品のため比較的安定。</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>5月末以降の入手が極めて困難。代替品でも90日以上のリードタイム</t>
+          <t>マレーシア生産品：通常6〜8週→12〜16週に延長。一部メーカーは新規受注停止中。</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>マレーシアリンギット対円：¥155/USD水準で輸入コスト+15〜20%の為替影響。</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>+50〜62%</t>
+          <t>+50〜70%（原料高+北米転換による供給減+運賃+為替）</t>
         </is>
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>食品加工・医療向けの需要は非弾力的（代替困難）</t>
+          <t>食品製造・医療・介護向けに需要は不変。供給不足が深刻で争奪戦状態。</t>
         </is>
       </c>
       <c r="P9" s="17" t="inlineStr">
         <is>
-          <t>医療機器規制上、代替品の切替えに認証が必要な場合あり</t>
+          <t>食品衛生法に基づく食品用手袋の規格要確認。代替品は規格適合品のみ採用可。</t>
         </is>
       </c>
       <c r="Q9" s="17" t="inlineStr">
         <is>
-          <t>同業他社が在庫を抱え込み。スポット市場での調達がほぼ不可能</t>
+          <t>同業他社も調達困難。一部卸売業者が高値転売・在庫抱え込みの動き。</t>
         </is>
       </c>
       <c r="R9" s="14" t="inlineStr">
         <is>
-          <t>食品加工・外食・医療取引先への緊急供給状況通知と価格改定を即時実施</t>
+          <t>食品製造・量販店向けの安定供給が最重要課題。供給不足による顧客離れリスクあり。</t>
         </is>
       </c>
       <c r="S9" s="14" t="inlineStr">
         <is>
-          <t>5ヶ月分以上の緊急積み増しが最優先。5月末まで日次在庫管理</t>
+          <t>在庫は2〜3週分（危機的水準）。至急3〜4ヶ月分の先行確保が必要。</t>
         </is>
       </c>
       <c r="T9" s="14" t="inlineStr">
         <is>
-          <t>Ansell・SRITEX・Hartalegaへの緊急発注を本日中に完了。主要顧客への供給状況説明会を今週開催</t>
+          <t>【最優先・緊急】Top Glove・Hartanega等マレーシアメーカーへの6〜9月分の長期購買契約を今週中に交渉・締結。現在庫の優先顧客への配分ルール策定。PVC・天然ゴム手袋の代替品在庫を同時に確保。価格改定通知を即時発送。</t>
         </is>
       </c>
       <c r="U9" s="31" t="inlineStr">
@@ -1602,17 +1617,17 @@
       </c>
       <c r="V9" s="17" t="inlineStr">
         <is>
-          <t>Malay Mail、KFF Health News、化学工業日報、Bloomberg</t>
+          <t>Top Glove・Hartalega IR 2026Q1、マレーシア手袋業界協会（MARGMA）、日本ゴム輸出入協会、化学工業日報2026年5月</t>
         </is>
       </c>
       <c r="W9" s="17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X9" s="17" t="inlineStr">
         <is>
-          <t>5月末の在庫枯渇が確実視される最重要案件。経営判断として在庫確保に最大限の予算配分を推奨</t>
+          <t>供給逼迫が最も深刻な商品。北米市場への転換により日本向け供給が▼60〜70%。3〜4ヶ月分の先行確保が最優先。</t>
         </is>
       </c>
     </row>
@@ -1629,112 +1644,112 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>PP・HDPE樹脂ともにナフサ連動で+42%まで上昇</t>
+          <t>PP・HDPE原料：旭化成PE全製品+120円/kg値上げ実施、PP・HDPE も同傾向。前期比+30〜40%の価格上昇。</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>仕入値+38〜48%見込み。岐阜プラスチックが5月出荷分の値上げを正式通知</t>
+          <t>食品用プラコンテナー：5月から+15〜22%値上げ。食品製造・物流向けに需要は底堅い。</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>岐阜プラスチック等（PP・HDPE樹脂は中東依存60〜70%）</t>
+          <t>住友化学・三井化学・旭化成（国産PP・HDPE）。一部は中国・台湾製輸入品。</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>北米産PP・HDPEの代替調達：LyondellBasellと価格交渉中</t>
+          <t>ステンレス製・アルミ製コンテナー（高価格・重量増）。再生PP製（食品用途は要規格確認）。</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>深刻継続。中東産PP・HDPE樹脂の供給制限が拡大</t>
+          <t>PP・HDPE原料がナフサ由来。ホルムズ封鎖→ナフサ高騰→樹脂価格+30〜40%直撃。</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>ホルムズ封鎖継続により中東産ポリオレフィン供給減少が続く</t>
+          <t>中東産ナフサ代替調達（米国・東南アジア産）も価格高騰・運賃増。</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>PP・HDPE→プロピレン・エチレン→ナフサ連動。ナフサ+48%直撃</t>
+          <t>エチレン→HDPE、プロピレン→PPの製造ライン。ナフサ+48%が直接原価に反映。</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>タンカー運賃が前週比さらに上昇</t>
+          <t>中国・台湾製輸入品：アジア発着運賃+50〜70%。国産品シフトが進む。</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>+8〜12%</t>
+          <t>重量物のため軽油価格上昇で配送コスト+12〜15%。</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>3ヶ月以上の遅延リスク継続</t>
+          <t>国内メーカーで通常4週→6〜8週に延長。輸入品は10〜12週。</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>円安¥158でさらに悪化</t>
+          <t>¥155/USD水準で輸入品コスト+15〜20%、国産品の輸入原料分も+10〜15%影響。</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
-          <t>+42〜52%</t>
+          <t>+25〜35%（原料高+運賃+為替）</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>食品加工・惣菜・農産物向け需要は安定。代替素材（紙製・バイオ）の問い合わせ増加</t>
+          <t>食品製造・物流・農業向けに需要は安定。長寿命・繰り返し使用のため買い替えサイクルは3〜5年。</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>プラ削減規制による代替需要も増加傾向</t>
+          <t>食品接触材料の安全規制（食品衛生法）対応品のみ採用可。再生材の使用比率に制限あり。</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>LyondellBasellへのアクセス競争が激化</t>
+          <t>岐阜プラスチック・積水化学等が値上げ実施。市場全体で価格転嫁進行中。</t>
         </is>
       </c>
       <c r="R10" s="14" t="inlineStr">
         <is>
-          <t>惣菜・農産物取引先に5月価格改定通知を今週発送。バイオPP製コンテナのサンプル提供開始</t>
+          <t>食品製造・物流各社への価格改定通知が必要。長期使用製品のため顧客理解は得やすい。</t>
         </is>
       </c>
       <c r="S10" s="14" t="inlineStr">
         <is>
-          <t>4ヶ月分以上の積み増しが急務</t>
+          <t>在庫は5〜6週分（比較的良好）。追加確保よりも価格転嫁対応が優先。</t>
         </is>
       </c>
       <c r="T10" s="14" t="inlineStr">
         <is>
-          <t>LyondellBasell北米産PPとの長期契約を今週中に締結。バイオPP製コンテナのサンプルを主要3社に提供</t>
-        </is>
-      </c>
-      <c r="U10" s="31" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>住友化学・三井化学への6月分PP・HDPE発注を今週確定。輸入品から国産品へのシフト検討。主要顧客への価格改定通知を5月末までに完了。</t>
+        </is>
+      </c>
+      <c r="U10" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="V10" s="16" t="inlineStr">
         <is>
-          <t>Plastics News、化学工業日報、石油化学工業協会</t>
+          <t>旭化成・住友化学・三井化学値上げ通知、岐阜プラスチックIR、化学工業日報2026年5月</t>
         </is>
       </c>
       <c r="W10" s="16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>プラ削減規制対応のバイオ素材提案が差別化につながる可能性がある</t>
+          <t>発泡スチロール・食品トレーと比較すると在庫余裕あり。価格転嫁対応を優先しつつ在庫水準を維持。</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1917,12 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t>石油系製品と比較すると影響は軽微。価格転嫁交渉は進展中</t>
+          <t>ホルムズ影響は間接的。燃料費・物流コスト増が主な価格上昇要因。</t>
         </is>
       </c>
       <c r="L3" s="22" t="inlineStr">
         <is>
-          <t>5月の価格改定を予定通り実施。燃料サーチャージ明細を顧客に提示し透明性を確保</t>
+          <t>5月末までに主要顧客への価格改定通知を完了。複数サプライヤーとの在庫確保契約を締結。</t>
         </is>
       </c>
       <c r="M3" s="23" t="inlineStr"/>
@@ -1950,12 +1965,12 @@
       </c>
       <c r="K4" s="22" t="inlineStr">
         <is>
-          <t>5月以降の供給不足が確実視される。代替品提案で顧客離れを防止</t>
+          <t>ホルムズ封鎖の直撃商品。原料チェーンが中東ナフサに直結。6月以降更なる値上げ可能性あり。</t>
         </is>
       </c>
       <c r="L4" s="22" t="inlineStr">
         <is>
-          <t>Styrolutionとの北米代替調達を今週中に決定。3ヶ月以上の在庫確保を優先。5月値上げ通知を顧客に発送</t>
+          <t>【緊急】今週中にPSジャパン・東洋スチレンに4〜6月分の発注量を確定。在庫を6週分に積増し。顧客への価格改定通知を5月15日までに完了。</t>
         </is>
       </c>
       <c r="M4" s="23" t="inlineStr"/>
@@ -1998,12 +2013,12 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>顧客側の代替需要獲得チャンスでもある。代替品提案を積極化</t>
+          <t>発泡スチロールと同様にナフサ直撃商品。スーパー向け納入比率が高いため早急な価格交渉が必要。</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
         <is>
-          <t>エフピコとの在庫確保交渉を本週完了。バガス製トレーのサンプルを主要5社に提供。価格改定通知を全顧客に発送</t>
+          <t>【緊急】主要樹脂メーカーへの6月分発注を今週中に確定。エフピコ等複数ソースへの分散調達体制強化。価格改定通知を5月20日までに発送。</t>
         </is>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
@@ -2046,12 +2061,12 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>北米代替品の価格は中東産比+5〜8%の見込み。コスト上昇は避けられないが供給安定化を優先</t>
+          <t>旭化成の+120円/kg値上げは即座に原価影響。6月以降の追加値上げも想定し先行在庫確保が必要。</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
         <is>
-          <t>ExxonMobil北米産LDPEの価格交渉を今週中に決着。生分解性ボードン袋のサンプル調達も並行実施</t>
+          <t>旭化成・丸紅への6月分ボードン袋原料発注を今週確定。バイオPE試作品の顧客提案を5月中に開始。価格改定通知を5月15日までに発送。</t>
         </is>
       </c>
       <c r="M6" s="23" t="inlineStr"/>
@@ -2081,25 +2096,25 @@
       <c r="E7" s="21" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="H7" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>北米産への切替えは完了まで4〜8週間。5月末までの在庫ブリッジが鍵</t>
+          <t>中東産輸入LLDPEの代替調達が急務。国内在庫確保により短期的な供給安定化は可能。</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
         <is>
-          <t>Dowとの長期契約を本週中に締結。宇部興産への在庫積み増しも並行して依頼</t>
+          <t>旭化成・東ソーへの6月分LLDPE発注を今週確定。積水化学との安定供給契約締結を5月末までに完了。価格改定通知を5月20日までに発送。</t>
         </is>
       </c>
       <c r="M7" s="23" t="inlineStr"/>
@@ -2142,12 +2157,12 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>5月末の在庫枯渇が確実視される最重要案件。経営判断として在庫確保に最大限の予算配分を推奨</t>
+          <t>供給逼迫が最も深刻な商品。北米市場への転換により日本向け供給が▼60〜70%。3〜4ヶ月分の先行確保が最優先。</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
         <is>
-          <t>Ansell・SRITEX・Hartalegaへの緊急発注を本日中に完了。主要顧客への供給状況説明会を今週開催</t>
+          <t>【最優先・緊急】Top Glove・Hartanega等マレーシアメーカーへの6〜9月分の長期購買契約を今週中に交渉・締結。現在庫の優先顧客への配分ルール策定。PVC・天然ゴム手袋の代替品在庫を同時に確保。価格改定通知を即時発送。</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr"/>
@@ -2177,25 +2192,25 @@
       <c r="E9" s="21" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
       <c r="G9" s="21" t="inlineStr"/>
-      <c r="H9" s="31" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>プラ削減規制対応のバイオ素材提案が差別化につながる可能性がある</t>
+          <t>発泡スチロール・食品トレーと比較すると在庫余裕あり。価格転嫁対応を優先しつつ在庫水準を維持。</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
         <is>
-          <t>LyondellBasell北米産PPとの長期契約を今週中に締結。バイオPP製コンテナのサンプルを主要3社に提供</t>
+          <t>住友化学・三井化学への6月分PP・HDPE発注を今週確定。輸入品から国産品へのシフト検討。主要顧客への価格改定通知を5月末までに完了。</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr"/>
